--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1077,130 +1077,130 @@
     <t>Round 1 - Match 1</t>
   </si>
   <si>
+    <t>Round 1 - Match 15</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
     <t>Round 1 - Match 16</t>
   </si>
   <si>
-    <t>Round 1 - Match 2</t>
+    <t>Round 1 - Match 3</t>
   </si>
   <si>
     <t>Round 1 - Match 17</t>
   </si>
   <si>
-    <t>Round 1 - Match 3</t>
+    <t>Round 1 - Match 4</t>
   </si>
   <si>
     <t>Round 1 - Match 18</t>
   </si>
   <si>
-    <t>Round 1 - Match 4</t>
+    <t>Round 1 - Match 5</t>
   </si>
   <si>
     <t>Round 1 - Match 19</t>
   </si>
   <si>
-    <t>Round 1 - Match 5</t>
+    <t>Round 1 - Match 6</t>
   </si>
   <si>
     <t>Round 1 - Match 20</t>
   </si>
   <si>
-    <t>Round 1 - Match 6</t>
+    <t>Round 1 - Match 7</t>
   </si>
   <si>
     <t>Round 1 - Match 21</t>
   </si>
   <si>
-    <t>Round 1 - Match 7</t>
+    <t>Round 1 - Match 8</t>
   </si>
   <si>
     <t>Round 1 - Match 22</t>
   </si>
   <si>
-    <t>Round 1 - Match 8</t>
+    <t>Round 1 - Match 9</t>
   </si>
   <si>
     <t>Round 1 - Match 23</t>
   </si>
   <si>
-    <t>Round 1 - Match 9</t>
+    <t>Round 1 - Match 10</t>
   </si>
   <si>
     <t>Round 1 - Match 24</t>
   </si>
   <si>
-    <t>Round 1 - Match 10</t>
+    <t>Round 1 - Match 11</t>
   </si>
   <si>
     <t>Round 1 - Match 25</t>
   </si>
   <si>
-    <t>Round 1 - Match 11</t>
+    <t>Round 1 - Match 12</t>
   </si>
   <si>
     <t>Round 1 - Match 26</t>
   </si>
   <si>
-    <t>Round 1 - Match 12</t>
+    <t>Round 1 - Match 13</t>
   </si>
   <si>
     <t>Round 1 - Match 27</t>
   </si>
   <si>
-    <t>Round 1 - Match 13</t>
+    <t>Round 1 - Match 14</t>
   </si>
   <si>
     <t>Round 1 - Match 28</t>
   </si>
   <si>
-    <t>Round 1 - Match 14</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 29</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 15</t>
-  </si>
-  <si>
-    <t>Round 1 - Match 30</t>
+    <t>Round 2 - Match 29</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 37</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 30</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 38</t>
   </si>
   <si>
     <t>Round 2 - Match 31</t>
   </si>
   <si>
-    <t>Round 2 - Match 38</t>
+    <t>Round 2 - Match 39</t>
   </si>
   <si>
     <t>Round 2 - Match 32</t>
   </si>
   <si>
-    <t>Round 2 - Match 39</t>
+    <t>Round 2 - Match 40</t>
   </si>
   <si>
     <t>Round 2 - Match 33</t>
   </si>
   <si>
-    <t>Round 2 - Match 40</t>
+    <t>Round 2 - Match 41</t>
   </si>
   <si>
     <t>Round 2 - Match 34</t>
   </si>
   <si>
-    <t>Round 2 - Match 41</t>
+    <t>Round 2 - Match 42</t>
   </si>
   <si>
     <t>Round 2 - Match 35</t>
   </si>
   <si>
-    <t>Round 2 - Match 42</t>
+    <t>Round 2 - Match 43</t>
   </si>
   <si>
     <t>Round 2 - Match 36</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 43</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 37</t>
   </si>
   <si>
     <t>Round 2 - Match 44</t>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -3521,7 +3521,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -3605,7 +3605,7 @@
         <f>data!$E$56&amp;" "&amp;data!$B$56</f>
       </c>
       <c r="G16" s="21">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -3625,7 +3625,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -3685,7 +3685,7 @@
         <f>'data'!$A$63</f>
       </c>
       <c r="G24" s="21">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -3771,7 +3771,7 @@
         <f>data!$E$66&amp;" "&amp;data!$B$66</f>
       </c>
       <c r="G32" s="21">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="D34" s="22"/>
       <c r="E34" s="21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="20"/>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D6" s="22"/>
       <c r="E6" s="21">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -3916,7 +3916,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="D10" s="22"/>
       <c r="E10" s="21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="20"/>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D14" s="22"/>
       <c r="E14" s="21">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I14" s="20"/>
       <c r="K14" s="20"/>
@@ -4000,7 +4000,7 @@
         <f>data!$E$80&amp;" "&amp;data!$B$80</f>
       </c>
       <c r="G16" s="21">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -4020,7 +4020,7 @@
       <c r="A18" s="22"/>
       <c r="D18" s="22"/>
       <c r="E18" s="21">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="20"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="D22" s="22"/>
       <c r="E22" s="21">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K22" s="20"/>
     </row>
@@ -4080,7 +4080,7 @@
         <f>'data'!$A$87</f>
       </c>
       <c r="G24" s="21">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D26" s="22"/>
       <c r="E26" s="21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" s="15"/>
       <c r="G26" s="20"/>
@@ -4133,18 +4133,16 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$90</f>
       </c>
-      <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O256)</f>
-      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>data!$E$88&amp;" "&amp;data!$B$88</f>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21">
-        <v>30</v>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="str">
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O256)</f>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -4152,27 +4150,35 @@
       <c r="A31" s="26" t="str">
         <f>data!$E$89&amp;" "&amp;data!$B$89</f>
       </c>
-      <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="str">
         <f>data!$E$90&amp;" "&amp;data!$B$90</f>
       </c>
+      <c r="G32" s="21">
+        <v>44</v>
+      </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33">
       <c r="A33" s="22"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$93</f>
       </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="str">
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="str">
@@ -13535,89 +13541,89 @@
       </c>
       <c r="O111" s="19"/>
     </row>
-    <row r="114">
-      <c r="A114" s="13" t="s">
+    <row r="119">
+      <c r="A119" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="B114" s="13"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="13"/>
-      <c r="I114" s="13" t="s">
+      <c r="B119" s="13"/>
+      <c r="C119" s="13"/>
+      <c r="D119" s="13"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
+      <c r="G119" s="13"/>
+      <c r="I119" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="J114" s="13"/>
-      <c r="K114" s="13"/>
-      <c r="L114" s="13"/>
-      <c r="M114" s="13"/>
-      <c r="N114" s="13"/>
-      <c r="O114" s="13"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="17" t="s">
+      <c r="J119" s="13"/>
+      <c r="K119" s="13"/>
+      <c r="L119" s="13"/>
+      <c r="M119" s="13"/>
+      <c r="N119" s="13"/>
+      <c r="O119" s="13"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="D115" s="14" t="s">
+      <c r="D120" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="G115" s="16" t="s">
+      <c r="G120" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="I115" s="17" t="s">
+      <c r="I120" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="L115" s="14" t="s">
+      <c r="L120" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="O115" s="16" t="s">
+      <c r="O120" s="16" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="14" t="str">
-        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O257)</f>
-      </c>
-      <c r="B116" s="18"/>
-      <c r="C116" s="18"/>
-      <c r="D116" s="18"/>
-      <c r="E116" s="18"/>
-      <c r="F116" s="18"/>
-      <c r="G116" s="14" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
-      </c>
-      <c r="I116" s="14" t="str">
-        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
-      </c>
-      <c r="J116" s="18"/>
-      <c r="K116" s="18"/>
-      <c r="L116" s="18"/>
-      <c r="M116" s="18"/>
-      <c r="N116" s="18"/>
-      <c r="O116" s="14" t="str">
-        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O256)</f>
-      </c>
-    </row>
-    <row r="118">
-      <c r="F118" t="s">
+    <row r="121">
+      <c r="A121" s="14" t="str">
+        <f>CONCATENATE("M 2 ",G14)</f>
+      </c>
+      <c r="B121" s="18"/>
+      <c r="C121" s="18"/>
+      <c r="D121" s="18"/>
+      <c r="E121" s="18"/>
+      <c r="F121" s="18"/>
+      <c r="G121" s="14" t="str">
+        <f>CONCATENATE("M 1 ",G6)</f>
+      </c>
+      <c r="I121" s="14" t="str">
+        <f>CONCATENATE("M 16 ",O14)</f>
+      </c>
+      <c r="J121" s="18"/>
+      <c r="K121" s="18"/>
+      <c r="L121" s="18"/>
+      <c r="M121" s="18"/>
+      <c r="N121" s="18"/>
+      <c r="O121" s="14" t="str">
+        <f>CONCATENATE("M 15 ",O6)</f>
+      </c>
+    </row>
+    <row r="123">
+      <c r="F123" t="s">
         <v>341</v>
       </c>
-      <c r="G118" s="19"/>
-      <c r="N118" t="s">
+      <c r="G123" s="19"/>
+      <c r="N123" t="s">
         <v>341</v>
       </c>
-      <c r="O118" s="19"/>
-    </row>
-    <row r="119">
-      <c r="F119" t="s">
+      <c r="O123" s="19"/>
+    </row>
+    <row r="124">
+      <c r="F124" t="s">
         <v>342</v>
       </c>
-      <c r="G119" s="19"/>
-      <c r="N119" t="s">
+      <c r="G124" s="19"/>
+      <c r="N124" t="s">
         <v>342</v>
       </c>
-      <c r="O119" s="19"/>
+      <c r="O124" s="19"/>
     </row>
     <row r="127">
       <c r="A127" s="13" t="s">
@@ -13661,7 +13667,7 @@
     </row>
     <row r="129">
       <c r="A129" s="14" t="str">
-        <f>CONCATENATE("M 2 ",G14)</f>
+        <f>CONCATENATE("M 4 ",G30)</f>
       </c>
       <c r="B129" s="18"/>
       <c r="C129" s="18"/>
@@ -13669,10 +13675,10 @@
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
       <c r="G129" s="14" t="str">
-        <f>CONCATENATE("M 1 ",G6)</f>
+        <f>CONCATENATE("M 3 ",G22)</f>
       </c>
       <c r="I129" s="14" t="str">
-        <f>CONCATENATE("M 17 ",O14)</f>
+        <f>CONCATENATE("M 18 ",O30)</f>
       </c>
       <c r="J129" s="18"/>
       <c r="K129" s="18"/>
@@ -13680,7 +13686,7 @@
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
       <c r="O129" s="14" t="str">
-        <f>CONCATENATE("M 16 ",O6)</f>
+        <f>CONCATENATE("M 17 ",O22)</f>
       </c>
     </row>
     <row r="131">
@@ -13745,7 +13751,7 @@
     </row>
     <row r="137">
       <c r="A137" s="14" t="str">
-        <f>CONCATENATE("M 4 ",G30)</f>
+        <f>CONCATENATE("M 6 ",G46)</f>
       </c>
       <c r="B137" s="18"/>
       <c r="C137" s="18"/>
@@ -13753,10 +13759,10 @@
       <c r="E137" s="18"/>
       <c r="F137" s="18"/>
       <c r="G137" s="14" t="str">
-        <f>CONCATENATE("M 3 ",G22)</f>
+        <f>CONCATENATE("M 5 ",G38)</f>
       </c>
       <c r="I137" s="14" t="str">
-        <f>CONCATENATE("M 19 ",O30)</f>
+        <f>CONCATENATE("M 20 ",O46)</f>
       </c>
       <c r="J137" s="18"/>
       <c r="K137" s="18"/>
@@ -13764,7 +13770,7 @@
       <c r="M137" s="18"/>
       <c r="N137" s="18"/>
       <c r="O137" s="14" t="str">
-        <f>CONCATENATE("M 18 ",O22)</f>
+        <f>CONCATENATE("M 19 ",O38)</f>
       </c>
     </row>
     <row r="139">
@@ -13829,7 +13835,7 @@
     </row>
     <row r="145">
       <c r="A145" s="14" t="str">
-        <f>CONCATENATE("M 6 ",G46)</f>
+        <f>CONCATENATE("M 8 ",G62)</f>
       </c>
       <c r="B145" s="18"/>
       <c r="C145" s="18"/>
@@ -13837,10 +13843,10 @@
       <c r="E145" s="18"/>
       <c r="F145" s="18"/>
       <c r="G145" s="14" t="str">
-        <f>CONCATENATE("M 5 ",G38)</f>
+        <f>CONCATENATE("M 7 ",G54)</f>
       </c>
       <c r="I145" s="14" t="str">
-        <f>CONCATENATE("M 21 ",O46)</f>
+        <f>CONCATENATE("M 22 ",O62)</f>
       </c>
       <c r="J145" s="18"/>
       <c r="K145" s="18"/>
@@ -13848,7 +13854,7 @@
       <c r="M145" s="18"/>
       <c r="N145" s="18"/>
       <c r="O145" s="14" t="str">
-        <f>CONCATENATE("M 20 ",O38)</f>
+        <f>CONCATENATE("M 21 ",O54)</f>
       </c>
     </row>
     <row r="147">
@@ -13913,7 +13919,7 @@
     </row>
     <row r="153">
       <c r="A153" s="14" t="str">
-        <f>CONCATENATE("M 8 ",G62)</f>
+        <f>CONCATENATE("M 10 ",G78)</f>
       </c>
       <c r="B153" s="18"/>
       <c r="C153" s="18"/>
@@ -13921,10 +13927,10 @@
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
       <c r="G153" s="14" t="str">
-        <f>CONCATENATE("M 7 ",G54)</f>
+        <f>CONCATENATE("M 9 ",G70)</f>
       </c>
       <c r="I153" s="14" t="str">
-        <f>CONCATENATE("M 23 ",O62)</f>
+        <f>CONCATENATE("M 24 ",O78)</f>
       </c>
       <c r="J153" s="18"/>
       <c r="K153" s="18"/>
@@ -13932,7 +13938,7 @@
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
       <c r="O153" s="14" t="str">
-        <f>CONCATENATE("M 22 ",O54)</f>
+        <f>CONCATENATE("M 23 ",O70)</f>
       </c>
     </row>
     <row r="155">
@@ -13997,7 +14003,7 @@
     </row>
     <row r="161">
       <c r="A161" s="14" t="str">
-        <f>CONCATENATE("M 10 ",G78)</f>
+        <f>CONCATENATE("M 12 ",G94)</f>
       </c>
       <c r="B161" s="18"/>
       <c r="C161" s="18"/>
@@ -14005,10 +14011,10 @@
       <c r="E161" s="18"/>
       <c r="F161" s="18"/>
       <c r="G161" s="14" t="str">
-        <f>CONCATENATE("M 9 ",G70)</f>
+        <f>CONCATENATE("M 11 ",G86)</f>
       </c>
       <c r="I161" s="14" t="str">
-        <f>CONCATENATE("M 25 ",O78)</f>
+        <f>CONCATENATE("M 26 ",O94)</f>
       </c>
       <c r="J161" s="18"/>
       <c r="K161" s="18"/>
@@ -14016,7 +14022,7 @@
       <c r="M161" s="18"/>
       <c r="N161" s="18"/>
       <c r="O161" s="14" t="str">
-        <f>CONCATENATE("M 24 ",O70)</f>
+        <f>CONCATENATE("M 25 ",O86)</f>
       </c>
     </row>
     <row r="163">
@@ -14081,7 +14087,7 @@
     </row>
     <row r="169">
       <c r="A169" s="14" t="str">
-        <f>CONCATENATE("M 12 ",G94)</f>
+        <f>CONCATENATE("M 14 ",G110)</f>
       </c>
       <c r="B169" s="18"/>
       <c r="C169" s="18"/>
@@ -14089,10 +14095,10 @@
       <c r="E169" s="18"/>
       <c r="F169" s="18"/>
       <c r="G169" s="14" t="str">
-        <f>CONCATENATE("M 11 ",G86)</f>
+        <f>CONCATENATE("M 13 ",G102)</f>
       </c>
       <c r="I169" s="14" t="str">
-        <f>CONCATENATE("M 27 ",O94)</f>
+        <f>CONCATENATE("M 28 ",O110)</f>
       </c>
       <c r="J169" s="18"/>
       <c r="K169" s="18"/>
@@ -14100,7 +14106,7 @@
       <c r="M169" s="18"/>
       <c r="N169" s="18"/>
       <c r="O169" s="14" t="str">
-        <f>CONCATENATE("M 26 ",O86)</f>
+        <f>CONCATENATE("M 27 ",O102)</f>
       </c>
     </row>
     <row r="171">
@@ -14165,7 +14171,7 @@
     </row>
     <row r="177">
       <c r="A177" s="14" t="str">
-        <f>CONCATENATE("M 14 ",G110)</f>
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O257)</f>
       </c>
       <c r="B177" s="18"/>
       <c r="C177" s="18"/>
@@ -14173,10 +14179,10 @@
       <c r="E177" s="18"/>
       <c r="F177" s="18"/>
       <c r="G177" s="14" t="str">
-        <f>CONCATENATE("M 13 ",G102)</f>
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
       </c>
       <c r="I177" s="14" t="str">
-        <f>CONCATENATE("M 29 ",O110)</f>
+        <f>CONCATENATE("Pool O-2nd ",'Pool Matches'!G257)</f>
       </c>
       <c r="J177" s="18"/>
       <c r="K177" s="18"/>
@@ -14184,7 +14190,7 @@
       <c r="M177" s="18"/>
       <c r="N177" s="18"/>
       <c r="O177" s="14" t="str">
-        <f>CONCATENATE("M 28 ",O102)</f>
+        <f>CONCATENATE("Pool AD-1st ",'Pool Matches'!O256)</f>
       </c>
     </row>
     <row r="179">
@@ -14249,7 +14255,7 @@
     </row>
     <row r="190">
       <c r="A190" s="14" t="str">
-        <f>CONCATENATE("M 32 ",G139)</f>
+        <f>CONCATENATE("M 30 ",G131)</f>
       </c>
       <c r="B190" s="18"/>
       <c r="C190" s="18"/>
@@ -14257,10 +14263,10 @@
       <c r="E190" s="18"/>
       <c r="F190" s="18"/>
       <c r="G190" s="14" t="str">
-        <f>CONCATENATE("M 31 ",G131)</f>
+        <f>CONCATENATE("M 29 ",G123)</f>
       </c>
       <c r="I190" s="14" t="str">
-        <f>CONCATENATE("M 39 ",O139)</f>
+        <f>CONCATENATE("M 38 ",O131)</f>
       </c>
       <c r="J190" s="18"/>
       <c r="K190" s="18"/>
@@ -14268,7 +14274,7 @@
       <c r="M190" s="18"/>
       <c r="N190" s="18"/>
       <c r="O190" s="14" t="str">
-        <f>CONCATENATE("M 38 ",O131)</f>
+        <f>CONCATENATE("M 37 ",O123)</f>
       </c>
     </row>
     <row r="192">
@@ -14333,7 +14339,7 @@
     </row>
     <row r="198">
       <c r="A198" s="14" t="str">
-        <f>CONCATENATE("M 34 ",G155)</f>
+        <f>CONCATENATE("M 32 ",G147)</f>
       </c>
       <c r="B198" s="18"/>
       <c r="C198" s="18"/>
@@ -14341,10 +14347,10 @@
       <c r="E198" s="18"/>
       <c r="F198" s="18"/>
       <c r="G198" s="14" t="str">
-        <f>CONCATENATE("M 33 ",G147)</f>
+        <f>CONCATENATE("M 31 ",G139)</f>
       </c>
       <c r="I198" s="14" t="str">
-        <f>CONCATENATE("M 41 ",O155)</f>
+        <f>CONCATENATE("M 40 ",O147)</f>
       </c>
       <c r="J198" s="18"/>
       <c r="K198" s="18"/>
@@ -14352,7 +14358,7 @@
       <c r="M198" s="18"/>
       <c r="N198" s="18"/>
       <c r="O198" s="14" t="str">
-        <f>CONCATENATE("M 40 ",O147)</f>
+        <f>CONCATENATE("M 39 ",O139)</f>
       </c>
     </row>
     <row r="200">
@@ -14417,7 +14423,7 @@
     </row>
     <row r="206">
       <c r="A206" s="14" t="str">
-        <f>CONCATENATE("M 36 ",G171)</f>
+        <f>CONCATENATE("M 34 ",G163)</f>
       </c>
       <c r="B206" s="18"/>
       <c r="C206" s="18"/>
@@ -14425,10 +14431,10 @@
       <c r="E206" s="18"/>
       <c r="F206" s="18"/>
       <c r="G206" s="14" t="str">
-        <f>CONCATENATE("M 35 ",G163)</f>
+        <f>CONCATENATE("M 33 ",G155)</f>
       </c>
       <c r="I206" s="14" t="str">
-        <f>CONCATENATE("M 43 ",O171)</f>
+        <f>CONCATENATE("M 42 ",O163)</f>
       </c>
       <c r="J206" s="18"/>
       <c r="K206" s="18"/>
@@ -14436,7 +14442,7 @@
       <c r="M206" s="18"/>
       <c r="N206" s="18"/>
       <c r="O206" s="14" t="str">
-        <f>CONCATENATE("M 42 ",O163)</f>
+        <f>CONCATENATE("M 41 ",O155)</f>
       </c>
     </row>
     <row r="208">
@@ -14501,7 +14507,7 @@
     </row>
     <row r="214">
       <c r="A214" s="14" t="str">
-        <f>CONCATENATE("M 15 ",G118)</f>
+        <f>CONCATENATE("M 36 ",G179)</f>
       </c>
       <c r="B214" s="18"/>
       <c r="C214" s="18"/>
@@ -14509,10 +14515,10 @@
       <c r="E214" s="18"/>
       <c r="F214" s="18"/>
       <c r="G214" s="14" t="str">
-        <f>CONCATENATE("M 37 ",G179)</f>
+        <f>CONCATENATE("M 35 ",G171)</f>
       </c>
       <c r="I214" s="14" t="str">
-        <f>CONCATENATE("M 30 ",O118)</f>
+        <f>CONCATENATE("M 44 ",O179)</f>
       </c>
       <c r="J214" s="18"/>
       <c r="K214" s="18"/>
@@ -14520,7 +14526,7 @@
       <c r="M214" s="18"/>
       <c r="N214" s="18"/>
       <c r="O214" s="14" t="str">
-        <f>CONCATENATE("M 44 ",O179)</f>
+        <f>CONCATENATE("M 43 ",O171)</f>
       </c>
     </row>
     <row r="216">
@@ -14875,8 +14881,8 @@
     <mergeCell ref="I98:O98"/>
     <mergeCell ref="A106:G106"/>
     <mergeCell ref="I106:O106"/>
-    <mergeCell ref="A114:G114"/>
-    <mergeCell ref="I114:O114"/>
+    <mergeCell ref="A119:G119"/>
+    <mergeCell ref="I119:O119"/>
     <mergeCell ref="A127:G127"/>
     <mergeCell ref="I127:O127"/>
     <mergeCell ref="A135:G135"/>
@@ -14912,10 +14918,10 @@
   <rowBreaks count="6" manualBreakCount="6">
     <brk id="41" max="16383" man="true"/>
     <brk id="81" max="16383" man="true"/>
-    <brk id="126" max="16383" man="true"/>
-    <brk id="166" max="16383" man="true"/>
-    <brk id="203" max="16383" man="true"/>
-    <brk id="245" max="16383" man="true"/>
+    <brk id="118" max="16383" man="true"/>
+    <brk id="158" max="16383" man="true"/>
+    <brk id="195" max="16383" man="true"/>
+    <brk id="232" max="16383" man="true"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="true"/>
@@ -14991,7 +14997,7 @@
         <f>data!$E$6&amp;" "&amp;data!$B$6</f>
       </c>
       <c r="G8" s="21">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -15073,7 +15079,7 @@
         <f>data!$E$10&amp;" "&amp;data!$B$10</f>
       </c>
       <c r="G16" s="21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -15153,7 +15159,7 @@
     <row r="24">
       <c r="A24" s="22"/>
       <c r="G24" s="21">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -15239,7 +15245,7 @@
         <f>data!$E$20&amp;" "&amp;data!$B$20</f>
       </c>
       <c r="G32" s="21">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
@@ -15389,7 +15395,7 @@
     <row r="8">
       <c r="A8" s="22"/>
       <c r="G8" s="21">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -15473,7 +15479,7 @@
         <f>data!$E$35&amp;" "&amp;data!$B$35</f>
       </c>
       <c r="G16" s="21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="20"/>
@@ -15553,7 +15559,7 @@
         <f>'data'!$A$42</f>
       </c>
       <c r="G24" s="21">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K24" s="20"/>
     </row>
@@ -15606,18 +15612,16 @@
       <c r="A29" s="24" t="str">
         <f>'data'!$A$45</f>
       </c>
-      <c r="C29" s="23" t="str">
-        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
-      </c>
       <c r="I29" s="20"/>
     </row>
     <row r="30">
       <c r="A30" s="25" t="str">
         <f>data!$E$43&amp;" "&amp;data!$B$43</f>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="21">
-        <v>15</v>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23" t="str">
+        <f>CONCATENATE("Pool O-1st ",'Pool Matches'!G256)</f>
       </c>
       <c r="I30" s="20"/>
     </row>
@@ -15625,27 +15629,35 @@
       <c r="A31" s="26" t="str">
         <f>data!$E$44&amp;" "&amp;data!$B$44</f>
       </c>
-      <c r="C31" s="23" t="str">
-        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O257)</f>
-      </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="20"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
       <c r="I31" s="20"/>
     </row>
     <row r="32">
       <c r="A32" s="27" t="str">
         <f>data!$E$45&amp;" "&amp;data!$B$45</f>
       </c>
+      <c r="G32" s="21">
+        <v>36</v>
+      </c>
       <c r="H32" s="15"/>
       <c r="I32" s="20"/>
     </row>
     <row r="33">
       <c r="A33" s="22"/>
+      <c r="G33" s="20"/>
     </row>
     <row r="34">
       <c r="A34" s="24" t="str">
         <f>'data'!$A$48</f>
       </c>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23" t="str">
+        <f>CONCATENATE("Pool AD-2nd ",'Pool Matches'!O257)</f>
+      </c>
+      <c r="F34" s="15"/>
+      <c r="G34" s="20"/>
     </row>
     <row r="35">
       <c r="A35" s="25" t="str">

--- a/pools-example-large-seeded.xlsx
+++ b/pools-example-large-seeded.xlsx
@@ -1282,94 +1282,94 @@
   </numFmts>
   <fonts count="13">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="16"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="16"/>
-      <u val="single"/>
     </font>
     <font>
+      <b val="1"/>
+      <u val="single"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="12"/>
-      <u val="single"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="28"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="72"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="72"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="12"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <i val="1"/>
-      <color/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="100"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="100"/>
     </font>
     <font>
+      <sz val="110"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="110"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="250"/>
+      <color/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color/>
-      <sz val="250"/>
     </font>
   </fonts>
   <fills count="6">
@@ -6069,16 +6069,16 @@
         <v>91</v>
       </c>
       <c r="D2" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E2" s="3" t="str">
         <f>(A2*B2*C2*D2)</f>
       </c>
       <c r="F2" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G2" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H2" s="31" t="str">
         <f>C2*I2+J2</f>
@@ -6095,16 +6095,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="3">
-        <v>0.0020833333333333333</v>
+        <v>0.00208333333333333</v>
       </c>
       <c r="E3" s="3" t="str">
         <f>(A3*B3*C3*D3)</f>
       </c>
       <c r="F3" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G3" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>E3+(A3*C3*F3)+G3</f>
@@ -6173,16 +6173,16 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3">
-        <v>0.002777777777777778</v>
+        <v>0.00277777777777777</v>
       </c>
       <c r="E8" s="3" t="str">
         <f>(A8*B8*D8)</f>
       </c>
       <c r="F8" s="3">
-        <v>0.00034722222222222224</v>
+        <v>0.000347222222222222</v>
       </c>
       <c r="G8" s="3">
-        <v>0.020833333333333332</v>
+        <v>0.0208333333333333</v>
       </c>
       <c r="H8" s="31" t="str">
         <f>E8+(A8*F8)+G8</f>
